--- a/data/AI_Adoption_Research_Data.xlsx
+++ b/data/AI_Adoption_Research_Data.xlsx
@@ -525,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Compiled: April 2026  |  Author: Mo  |  Course: Topic Check-in</t>
+          <t>Compiled: April 2026  |  Author: Mohamed Abdel-Hamid  |  Course: Topic Check-in</t>
         </is>
       </c>
     </row>
